--- a/週五精準預測成果/SENSITIVITY_ANALYSIS.xlsx
+++ b/週五精準預測成果/SENSITIVITY_ANALYSIS.xlsx
@@ -463,7 +463,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>109.5</t>
+          <t>130.8</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -472,7 +472,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>30.2</v>
+        <v>30.9</v>
       </c>
       <c r="E2" t="n">
         <v>-0.3</v>
@@ -486,7 +486,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>115.0</t>
+          <t>137.3</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -495,7 +495,7 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>31.2</v>
+        <v>31.9</v>
       </c>
       <c r="E3" t="n">
         <v>0.7</v>
@@ -509,7 +509,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>104.0</t>
+          <t>124.3</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -518,10 +518,10 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>29.3</v>
+        <v>29.9</v>
       </c>
       <c r="E4" t="n">
-        <v>-1.2</v>
+        <v>-1.3</v>
       </c>
     </row>
     <row r="5">
@@ -532,7 +532,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>109.5</t>
+          <t>130.8</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -541,7 +541,7 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>30.6</v>
+        <v>31.3</v>
       </c>
       <c r="E5" t="n">
         <v>0.1</v>
@@ -555,7 +555,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>109.5</t>
+          <t>130.8</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -564,10 +564,10 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>29.9</v>
+        <v>30.5</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.6</v>
+        <v>-0.7</v>
       </c>
     </row>
     <row r="7">
@@ -578,7 +578,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>115.0</t>
+          <t>137.3</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -587,10 +587,10 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>31.5</v>
+        <v>32.4</v>
       </c>
       <c r="E7" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
     </row>
   </sheetData>

--- a/週五精準預測成果/SENSITIVITY_ANALYSIS.xlsx
+++ b/週五精準預測成果/SENSITIVITY_ANALYSIS.xlsx
@@ -463,19 +463,19 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>130.8</t>
+          <t>114.9</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>31.6</t>
+          <t>31.8</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>30.9</v>
+        <v>30.8</v>
       </c>
       <c r="E2" t="n">
-        <v>-0.3</v>
+        <v>-0.4</v>
       </c>
     </row>
     <row r="3">
@@ -486,19 +486,19 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>137.3</t>
+          <t>120.6</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>31.6</t>
+          <t>31.8</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>31.9</v>
+        <v>31.8</v>
       </c>
       <c r="E3" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="4">
@@ -509,19 +509,19 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>124.3</t>
+          <t>109.1</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>31.6</t>
+          <t>31.8</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>29.9</v>
+        <v>29.8</v>
       </c>
       <c r="E4" t="n">
-        <v>-1.3</v>
+        <v>-1.4</v>
       </c>
     </row>
     <row r="5">
@@ -532,19 +532,19 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>130.8</t>
+          <t>114.9</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>32.3</t>
+          <t>32.5</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>31.3</v>
+        <v>31.2</v>
       </c>
       <c r="E5" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -555,19 +555,19 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>130.8</t>
+          <t>114.9</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>31.0</t>
+          <t>31.2</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>30.5</v>
+        <v>30.4</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.7</v>
+        <v>-0.8</v>
       </c>
     </row>
     <row r="7">
@@ -578,19 +578,19 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>137.3</t>
+          <t>120.6</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>32.3</t>
+          <t>32.5</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>32.4</v>
+        <v>32.2</v>
       </c>
       <c r="E7" t="n">
-        <v>1.2</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/週五精準預測成果/SENSITIVITY_ANALYSIS.xlsx
+++ b/週五精準預測成果/SENSITIVITY_ANALYSIS.xlsx
@@ -463,7 +463,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>114.9</t>
+          <t>114.0</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -486,7 +486,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>120.6</t>
+          <t>119.7</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -509,7 +509,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>109.1</t>
+          <t>108.3</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -532,7 +532,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>114.9</t>
+          <t>114.0</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -555,7 +555,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>114.9</t>
+          <t>114.0</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -578,7 +578,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>120.6</t>
+          <t>119.7</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">

--- a/週五精準預測成果/SENSITIVITY_ANALYSIS.xlsx
+++ b/週五精準預測成果/SENSITIVITY_ANALYSIS.xlsx
@@ -463,19 +463,19 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>114.0</t>
+          <t>125.4</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>31.8</t>
+          <t>32.0</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>30.8</v>
+        <v>31.5</v>
       </c>
       <c r="E2" t="n">
-        <v>-0.4</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="3">
@@ -486,19 +486,19 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>119.7</t>
+          <t>131.7</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>31.8</t>
+          <t>32.0</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>31.8</v>
+        <v>32.5</v>
       </c>
       <c r="E3" t="n">
-        <v>0.6</v>
+        <v>1.3</v>
       </c>
     </row>
     <row r="4">
@@ -509,19 +509,19 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>108.3</t>
+          <t>119.2</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>31.8</t>
+          <t>32.0</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>29.8</v>
+        <v>30.5</v>
       </c>
       <c r="E4" t="n">
-        <v>-1.4</v>
+        <v>-0.7</v>
       </c>
     </row>
     <row r="5">
@@ -532,19 +532,19 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>114.0</t>
+          <t>125.4</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>32.5</t>
+          <t>32.7</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>31.2</v>
+        <v>31.9</v>
       </c>
       <c r="E5" t="n">
-        <v>0</v>
+        <v>0.7</v>
       </c>
     </row>
     <row r="6">
@@ -555,19 +555,19 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>114.0</t>
+          <t>125.4</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>31.2</t>
+          <t>31.4</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>30.4</v>
+        <v>31.1</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.8</v>
+        <v>-0.1</v>
       </c>
     </row>
     <row r="7">
@@ -578,19 +578,19 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>119.7</t>
+          <t>131.7</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>32.5</t>
+          <t>32.7</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>32.2</v>
+        <v>33</v>
       </c>
       <c r="E7" t="n">
-        <v>1</v>
+        <v>1.8</v>
       </c>
     </row>
   </sheetData>

--- a/週五精準預測成果/SENSITIVITY_ANALYSIS.xlsx
+++ b/週五精準預測成果/SENSITIVITY_ANALYSIS.xlsx
@@ -463,19 +463,19 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>125.4</t>
+          <t>126.5</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>32.0</t>
+          <t>31.9</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>31.5</v>
+        <v>31.1</v>
       </c>
       <c r="E2" t="n">
-        <v>0.3</v>
+        <v>-0.1</v>
       </c>
     </row>
     <row r="3">
@@ -486,19 +486,19 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>131.7</t>
+          <t>132.9</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>32.0</t>
+          <t>31.9</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>32.5</v>
+        <v>32.1</v>
       </c>
       <c r="E3" t="n">
-        <v>1.3</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="4">
@@ -509,19 +509,19 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>119.2</t>
+          <t>120.2</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>32.0</t>
+          <t>31.9</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>30.5</v>
+        <v>30.1</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.7</v>
+        <v>-1.1</v>
       </c>
     </row>
     <row r="5">
@@ -532,19 +532,19 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>125.4</t>
+          <t>126.5</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>32.7</t>
+          <t>32.6</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>31.9</v>
+        <v>31.5</v>
       </c>
       <c r="E5" t="n">
-        <v>0.7</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="6">
@@ -555,19 +555,19 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>125.4</t>
+          <t>126.5</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>31.4</t>
+          <t>31.3</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>31.1</v>
+        <v>30.7</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.1</v>
+        <v>-0.5</v>
       </c>
     </row>
     <row r="7">
@@ -578,19 +578,19 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>131.7</t>
+          <t>132.9</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>32.7</t>
+          <t>32.6</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>33</v>
+        <v>32.5</v>
       </c>
       <c r="E7" t="n">
-        <v>1.8</v>
+        <v>1.3</v>
       </c>
     </row>
   </sheetData>

--- a/週五精準預測成果/SENSITIVITY_ANALYSIS.xlsx
+++ b/週五精準預測成果/SENSITIVITY_ANALYSIS.xlsx
@@ -463,19 +463,19 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>126.5</t>
+          <t>115.2</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>31.9</t>
+          <t>32.4</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>31.1</v>
+        <v>31.3</v>
       </c>
       <c r="E2" t="n">
-        <v>-0.1</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="3">
@@ -486,19 +486,19 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>132.9</t>
+          <t>121.0</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>31.9</t>
+          <t>32.4</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>32.1</v>
+        <v>32.3</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9</v>
+        <v>1.1</v>
       </c>
     </row>
     <row r="4">
@@ -509,19 +509,19 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>120.2</t>
+          <t>109.5</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>31.9</t>
+          <t>32.4</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>30.1</v>
+        <v>30.3</v>
       </c>
       <c r="E4" t="n">
-        <v>-1.1</v>
+        <v>-0.9</v>
       </c>
     </row>
     <row r="5">
@@ -532,19 +532,19 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>126.5</t>
+          <t>115.2</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>32.6</t>
+          <t>33.0</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>31.5</v>
+        <v>31.7</v>
       </c>
       <c r="E5" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="6">
@@ -555,19 +555,19 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>126.5</t>
+          <t>115.2</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>31.3</t>
+          <t>31.8</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>30.7</v>
+        <v>30.9</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.5</v>
+        <v>-0.3</v>
       </c>
     </row>
     <row r="7">
@@ -578,19 +578,19 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>132.9</t>
+          <t>121.0</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>32.6</t>
+          <t>33.0</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>32.5</v>
+        <v>32.7</v>
       </c>
       <c r="E7" t="n">
-        <v>1.3</v>
+        <v>1.5</v>
       </c>
     </row>
   </sheetData>

--- a/週五精準預測成果/SENSITIVITY_ANALYSIS.xlsx
+++ b/週五精準預測成果/SENSITIVITY_ANALYSIS.xlsx
@@ -463,19 +463,19 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>115.2</t>
+          <t>123.1</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>32.4</t>
+          <t>32.5</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>31.3</v>
+        <v>31.5</v>
       </c>
       <c r="E2" t="n">
-        <v>0.1</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="3">
@@ -486,19 +486,19 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>121.0</t>
+          <t>129.3</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>32.4</t>
+          <t>32.5</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>32.3</v>
+        <v>32.5</v>
       </c>
       <c r="E3" t="n">
-        <v>1.1</v>
+        <v>1.3</v>
       </c>
     </row>
     <row r="4">
@@ -509,19 +509,19 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>109.5</t>
+          <t>116.9</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>32.4</t>
+          <t>32.5</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>30.3</v>
+        <v>30.5</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.9</v>
+        <v>-0.7</v>
       </c>
     </row>
     <row r="5">
@@ -532,19 +532,19 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>115.2</t>
+          <t>123.1</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>33.0</t>
+          <t>33.2</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>31.7</v>
+        <v>32</v>
       </c>
       <c r="E5" t="n">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="6">
@@ -555,19 +555,19 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>115.2</t>
+          <t>123.1</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>31.8</t>
+          <t>31.9</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>30.9</v>
+        <v>31.1</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.3</v>
+        <v>-0.1</v>
       </c>
     </row>
     <row r="7">
@@ -578,19 +578,19 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>121.0</t>
+          <t>129.3</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>33.0</t>
+          <t>33.2</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>32.7</v>
+        <v>33</v>
       </c>
       <c r="E7" t="n">
-        <v>1.5</v>
+        <v>1.8</v>
       </c>
     </row>
   </sheetData>
